--- a/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260727_manha.xlsx
+++ b/dados/SURVEY_VESSELS/SURVEY_VESSELS_20260727_manha.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cefetrjbr-my.sharepoint.com/personal/12396387790_cefet-rj_br/Documents/Empresas e entrevistas/projeto logistica offshore/ofi/dados/SURVEY_VESSELS/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="85" documentId="8_{54908CC9-2D4B-42FA-A381-D5F9259AAA7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B0FCEF46-BBE8-4692-AEEA-81266EFE91C7}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" activeTab="3" xr2:uid="{FAEFD476-B005-4995-A964-6D919B2AA8E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -304,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -322,7 +322,6 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2161,7 +2160,6 @@
       <c r="F12" s="6">
         <v>46230.341666666667</v>
       </c>
-      <c r="G12" s="7"/>
       <c r="H12" s="1" t="s">
         <v>65</v>
       </c>
@@ -2185,7 +2183,6 @@
       <c r="F13" s="6">
         <v>46230.331250000003</v>
       </c>
-      <c r="G13" s="7"/>
       <c r="H13" s="1" t="s">
         <v>66</v>
       </c>
@@ -2209,7 +2206,6 @@
       <c r="F14" s="6">
         <v>46230.336805555555</v>
       </c>
-      <c r="G14" s="7"/>
       <c r="H14" s="1" t="s">
         <v>67</v>
       </c>
@@ -2232,7 +2228,6 @@
       <c r="F15" s="6">
         <v>46230.341666666667</v>
       </c>
-      <c r="G15" s="7"/>
       <c r="H15" s="1" t="s">
         <v>65</v>
       </c>
@@ -2255,7 +2250,6 @@
       <c r="F16" s="6">
         <v>46230.145833333336</v>
       </c>
-      <c r="G16" s="7"/>
       <c r="H16" s="1" t="s">
         <v>67</v>
       </c>
@@ -2278,7 +2272,6 @@
       <c r="F17" s="6">
         <v>46120.325694444444</v>
       </c>
-      <c r="G17" s="7"/>
       <c r="H17" s="1" t="s">
         <v>67</v>
       </c>
@@ -2301,7 +2294,6 @@
       <c r="F18" s="6">
         <v>46230.3</v>
       </c>
-      <c r="G18" s="7"/>
       <c r="H18" s="1" t="s">
         <v>67</v>
       </c>
